--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -566,22 +566,22 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12241</v>
+        <v>12287</v>
       </c>
       <c r="C2">
-        <v>14503</v>
+        <v>14564</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F2">
         <v>17.8</v>
       </c>
       <c r="G2">
-        <v>85568.66</v>
+        <v>85915.75</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>8014</v>
       </c>
       <c r="N2">
-        <v>8.9</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -610,22 +610,22 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2506</v>
+        <v>2521</v>
       </c>
       <c r="C3">
-        <v>2730</v>
+        <v>2747</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="F3">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="G3">
-        <v>15492.42</v>
+        <v>15588.3</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>1558</v>
       </c>
       <c r="N3">
-        <v>13.94</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -654,22 +654,22 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="C4">
-        <v>1094</v>
+        <v>1104</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F4">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="G4">
-        <v>7906.14</v>
+        <v>7971.44</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -690,7 +690,7 @@
         <v>679</v>
       </c>
       <c r="N4">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -698,22 +698,22 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="C5">
-        <v>868</v>
+        <v>878</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F5">
-        <v>76.8</v>
+        <v>76.2</v>
       </c>
       <c r="G5">
-        <v>7785.96</v>
+        <v>7875.66</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>479</v>
       </c>
       <c r="N5">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -771,22 +771,22 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="C7">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F7">
-        <v>63.3</v>
+        <v>62.2</v>
       </c>
       <c r="G7">
-        <v>3657.39</v>
+        <v>3781.77</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -807,7 +807,7 @@
         <v>222</v>
       </c>
       <c r="N7">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -815,22 +815,22 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>528</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>531</v>
+        <v>619</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="F8">
         <v>42.4</v>
       </c>
       <c r="G8">
-        <v>3207.24</v>
+        <v>3738.76</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -859,10 +859,10 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C9">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -871,10 +871,10 @@
         <v>242</v>
       </c>
       <c r="F9">
-        <v>80.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G9">
-        <v>1484.31</v>
+        <v>1494.03</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -895,7 +895,7 @@
         <v>184</v>
       </c>
       <c r="N9">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -903,10 +903,10 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -915,10 +915,10 @@
         <v>192</v>
       </c>
       <c r="F10">
-        <v>85</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G10">
-        <v>1073.71</v>
+        <v>1078.44</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>124</v>
       </c>
       <c r="N10">
-        <v>6.83</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1032,10 +1032,10 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -1044,13 +1044,13 @@
         <v>32</v>
       </c>
       <c r="F13">
-        <v>84.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1114,22 +1114,22 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="G15">
-        <v>106.35</v>
+        <v>113.44</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1158,10 +1158,10 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1170,13 +1170,13 @@
         <v>13</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -1276,16 +1276,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12241</v>
+        <v>12287</v>
       </c>
       <c r="C2">
-        <v>9406</v>
+        <v>9414</v>
       </c>
       <c r="D2">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="E2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F2">
         <v>279</v>
@@ -1294,7 +1294,7 @@
         <v>155</v>
       </c>
       <c r="H2">
-        <v>344</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1302,13 +1302,13 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2506</v>
+        <v>2521</v>
       </c>
       <c r="C3">
-        <v>1226</v>
+        <v>1236</v>
       </c>
       <c r="D3">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E3">
         <v>146</v>
@@ -1320,7 +1320,7 @@
         <v>56</v>
       </c>
       <c r="H3">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1328,13 +1328,13 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="C4">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="D4">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E4">
         <v>68</v>
@@ -1346,7 +1346,7 @@
         <v>32</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="C5">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D5">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E5">
         <v>40</v>
@@ -1372,7 +1372,7 @@
         <v>22</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1406,25 +1406,25 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="C7">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="D7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E7">
         <v>36</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7">
         <v>15</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1432,25 +1432,25 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>528</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="D8">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="E8">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F8">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1458,19 +1458,19 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C9">
         <v>82</v>
       </c>
       <c r="D9">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9">
         <v>42</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9">
         <v>22</v>
@@ -1484,10 +1484,10 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10">
         <v>99</v>
@@ -1562,7 +1562,7 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1580,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1614,7 +1614,7 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>2</v>
@@ -1640,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1649,7 +1649,7 @@
         <v>4</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -1743,13 +1743,13 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12241</v>
+        <v>12287</v>
       </c>
       <c r="C2">
-        <v>9244</v>
+        <v>9245</v>
       </c>
       <c r="D2">
-        <v>75.5</v>
+        <v>75.2</v>
       </c>
       <c r="E2">
         <v>5074</v>
@@ -1758,7 +1758,7 @@
         <v>2208</v>
       </c>
       <c r="G2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="H2">
         <v>117</v>
@@ -1776,7 +1776,7 @@
         <v>1999</v>
       </c>
       <c r="M2">
-        <v>998</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1784,22 +1784,22 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2506</v>
+        <v>2521</v>
       </c>
       <c r="C3">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="D3">
-        <v>61.3</v>
+        <v>61.1</v>
       </c>
       <c r="E3">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="F3">
         <v>581</v>
       </c>
       <c r="G3">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H3">
         <v>9</v>
@@ -1814,10 +1814,10 @@
         <v>12</v>
       </c>
       <c r="L3">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M3">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1825,22 +1825,22 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1043</v>
+        <v>1053</v>
       </c>
       <c r="C4">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="D4">
-        <v>63.8</v>
+        <v>63.6</v>
       </c>
       <c r="E4">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F4">
         <v>137</v>
       </c>
       <c r="G4">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -1858,7 +1858,7 @@
         <v>209</v>
       </c>
       <c r="M4">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1866,19 +1866,19 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="C5">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D5">
-        <v>63.5</v>
+        <v>63</v>
       </c>
       <c r="E5">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F5">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G5">
         <v>80</v>
@@ -1896,10 +1896,10 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M5">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1948,19 +1948,19 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="C7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D7">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="E7">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F7">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G7">
         <v>55</v>
@@ -1969,7 +1969,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7">
         <v>18</v>
@@ -1978,10 +1978,10 @@
         <v>4</v>
       </c>
       <c r="L7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M7">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1989,40 +1989,40 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>528</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="D8">
-        <v>39.8</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>9</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="M8">
-        <v>276</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2030,22 +2030,22 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C9">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D9">
-        <v>66.8</v>
+        <v>67</v>
       </c>
       <c r="E9">
         <v>70</v>
       </c>
       <c r="F9">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -2071,19 +2071,19 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D10">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="E10">
         <v>52</v>
       </c>
       <c r="F10">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G10">
         <v>22</v>
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>22</v>
       </c>
       <c r="D13">
-        <v>57.9</v>
+        <v>56.4</v>
       </c>
       <c r="E13">
         <v>12</v>
@@ -2227,7 +2227,7 @@
         <v>5</v>
       </c>
       <c r="M13">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2276,13 +2276,13 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>11</v>
       </c>
       <c r="D15">
-        <v>73.3</v>
+        <v>68.8</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -2309,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2317,13 +2317,13 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>10</v>
       </c>
       <c r="D16">
-        <v>76.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16">
         <v>3</v>

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
   <si>
     <t>product</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Gut Shift</t>
   </si>
   <si>
-    <t>Lemon Ginger</t>
-  </si>
-  <si>
     <t>Skin Radiance</t>
   </si>
   <si>
@@ -90,13 +87,13 @@
     <t>Ashwagandha Capsules</t>
   </si>
   <si>
+    <t>Shatavari</t>
+  </si>
+  <si>
+    <t>Moringa</t>
+  </si>
+  <si>
     <t>Frother</t>
-  </si>
-  <si>
-    <t>Shatavari</t>
-  </si>
-  <si>
-    <t>Moringa</t>
   </si>
   <si>
     <t>Matcha</t>
@@ -514,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -566,22 +563,22 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12287</v>
+        <v>12072</v>
       </c>
       <c r="C2">
-        <v>14564</v>
+        <v>14325</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>2178</v>
+        <v>2047</v>
       </c>
       <c r="F2">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>85915.75</v>
+        <v>84463.36</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -590,19 +587,19 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>760702.3100000001</v>
+        <v>758556.46</v>
       </c>
       <c r="K2">
-        <v>21428</v>
+        <v>21363</v>
       </c>
       <c r="L2">
-        <v>28159</v>
+        <v>27697</v>
       </c>
       <c r="M2">
-        <v>8015</v>
+        <v>7966</v>
       </c>
       <c r="N2">
-        <v>8.85</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -610,22 +607,22 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2521</v>
+        <v>2142</v>
       </c>
       <c r="C3">
-        <v>2747</v>
+        <v>2357</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>1245</v>
+        <v>1198</v>
       </c>
       <c r="F3">
-        <v>49.4</v>
+        <v>55.9</v>
       </c>
       <c r="G3">
-        <v>15588.3</v>
+        <v>13357.47</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -634,19 +631,19 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>216622.54</v>
+        <v>214284.85</v>
       </c>
       <c r="K3">
-        <v>7905</v>
+        <v>7814</v>
       </c>
       <c r="L3">
-        <v>5011</v>
+        <v>4955</v>
       </c>
       <c r="M3">
-        <v>1550</v>
+        <v>1535</v>
       </c>
       <c r="N3">
-        <v>13.9</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -654,22 +651,22 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C4">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="F4">
-        <v>44.6</v>
+        <v>43.7</v>
       </c>
       <c r="G4">
-        <v>7971.44</v>
+        <v>7958.38</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -678,19 +675,19 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>21986.67</v>
+        <v>21750.76</v>
       </c>
       <c r="K4">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="L4">
-        <v>1775</v>
+        <v>1764</v>
       </c>
       <c r="M4">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="N4">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -707,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>658</v>
+        <v>630</v>
       </c>
       <c r="F5">
-        <v>76.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="G5">
         <v>7875.66</v>
@@ -722,19 +719,19 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>27897.08</v>
+        <v>27829.21</v>
       </c>
       <c r="K5">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="L5">
-        <v>990</v>
+        <v>928</v>
       </c>
       <c r="M5">
-        <v>479</v>
+        <v>439</v>
       </c>
       <c r="N5">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -742,28 +739,43 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>717</v>
+        <v>621</v>
       </c>
       <c r="C6">
-        <v>723</v>
+        <v>627</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>396</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>63.8</v>
       </c>
       <c r="G6">
-        <v>3470.4</v>
+        <v>3781.77</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>718.23</v>
+      </c>
+      <c r="K6">
+        <v>44</v>
+      </c>
+      <c r="L6">
+        <v>342</v>
+      </c>
+      <c r="M6">
+        <v>236</v>
+      </c>
+      <c r="N6">
+        <v>0.19</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -771,22 +783,22 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C7">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>401</v>
+        <v>265</v>
       </c>
       <c r="F7">
-        <v>64.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="G7">
-        <v>3781.77</v>
+        <v>3738.76</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -795,19 +807,19 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>718.23</v>
+        <v>107.47</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>362</v>
+        <v>67</v>
       </c>
       <c r="M7">
-        <v>245</v>
+        <v>50</v>
       </c>
       <c r="N7">
-        <v>0.19</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -815,22 +827,22 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>615</v>
+        <v>303</v>
       </c>
       <c r="C8">
-        <v>619</v>
+        <v>307</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>266</v>
+        <v>233</v>
       </c>
       <c r="F8">
-        <v>43.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G8">
-        <v>3738.76</v>
+        <v>1494.03</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -839,19 +851,19 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>107.47</v>
+        <v>7461.57</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>699</v>
       </c>
       <c r="L8">
-        <v>67</v>
+        <v>460</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="N8">
-        <v>0.03</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -859,22 +871,22 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="C9">
-        <v>307</v>
+        <v>228</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="F9">
-        <v>79.2</v>
+        <v>83.7</v>
       </c>
       <c r="G9">
-        <v>1494.03</v>
+        <v>1078.44</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -883,19 +895,19 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>7474.21</v>
+        <v>6637.33</v>
       </c>
       <c r="K9">
-        <v>700</v>
+        <v>593</v>
       </c>
       <c r="L9">
-        <v>484</v>
+        <v>324</v>
       </c>
       <c r="M9">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -903,22 +915,22 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="C10">
-        <v>228</v>
+        <v>85</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>192</v>
+        <v>29</v>
       </c>
       <c r="F10">
-        <v>84.59999999999999</v>
+        <v>35.8</v>
       </c>
       <c r="G10">
-        <v>1078.44</v>
+        <v>610.9</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -927,19 +939,19 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>6637.04</v>
+        <v>1353.35</v>
       </c>
       <c r="K10">
-        <v>593</v>
+        <v>46</v>
       </c>
       <c r="L10">
-        <v>325</v>
+        <v>146</v>
       </c>
       <c r="M10">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="N10">
-        <v>6.15</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -947,43 +959,40 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C11">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>37</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G11">
-        <v>610.9</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>1353.35</v>
+        <v>94.11</v>
       </c>
       <c r="K11">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="M11">
-        <v>66</v>
-      </c>
-      <c r="N11">
-        <v>2.22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -991,40 +1000,40 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>25.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
       <c r="J12">
-        <v>26.97</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1032,40 +1041,40 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F13">
-        <v>82.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>94.11</v>
+        <v>26.97</v>
       </c>
       <c r="K13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M13">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1073,25 +1082,25 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F14">
-        <v>77.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>113.44</v>
       </c>
       <c r="H14">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -1103,10 +1112,13 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1114,26 +1126,26 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>14</v>
       </c>
-      <c r="F15">
-        <v>87.5</v>
-      </c>
-      <c r="G15">
-        <v>113.44</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
       <c r="I15" t="b">
         <v>1</v>
       </c>
@@ -1144,13 +1156,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>8</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1158,25 +1167,25 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F16">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -1188,50 +1197,9 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>7</v>
-      </c>
-      <c r="F17">
-        <v>100</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>7</v>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>3</v>
-      </c>
-      <c r="M17">
         <v>3</v>
       </c>
     </row>
@@ -1242,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1253,22 +1221,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1276,25 +1244,25 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12287</v>
+        <v>12072</v>
       </c>
       <c r="C2">
-        <v>9436</v>
+        <v>9397</v>
       </c>
       <c r="D2">
-        <v>1667</v>
+        <v>1693</v>
       </c>
       <c r="E2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="F2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G2">
         <v>155</v>
       </c>
       <c r="H2">
-        <v>354</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1302,25 +1270,25 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2521</v>
+        <v>2142</v>
       </c>
       <c r="C3">
-        <v>1238</v>
+        <v>1185</v>
       </c>
       <c r="D3">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="E3">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F3">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3">
         <v>56</v>
       </c>
       <c r="H3">
-        <v>366</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1328,16 +1296,16 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C4">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D4">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>43</v>
@@ -1346,7 +1314,7 @@
         <v>32</v>
       </c>
       <c r="H4">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1357,22 +1325,22 @@
         <v>865</v>
       </c>
       <c r="C5">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="D5">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>22</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1380,25 +1348,25 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>717</v>
+        <v>621</v>
       </c>
       <c r="C6">
-        <v>112</v>
+        <v>317</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>603</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1406,25 +1374,25 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C7">
-        <v>320</v>
+        <v>102</v>
       </c>
       <c r="D7">
-        <v>215</v>
+        <v>289</v>
       </c>
       <c r="E7">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H7">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1432,25 +1400,25 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>615</v>
+        <v>303</v>
       </c>
       <c r="C8">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D8">
-        <v>280</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="F8">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="G8">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1458,25 +1426,25 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="C9">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="E9">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1484,25 +1452,25 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="C10">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="D10">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1510,22 +1478,22 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C11">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1536,25 +1504,25 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>2</v>
       </c>
       <c r="H12">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1562,25 +1530,25 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
         <v>6</v>
       </c>
-      <c r="D13">
-        <v>23</v>
-      </c>
-      <c r="E13">
-        <v>4</v>
-      </c>
       <c r="F13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1588,16 +1556,16 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>10</v>
       </c>
-      <c r="D14">
-        <v>13</v>
-      </c>
       <c r="E14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -1614,22 +1582,22 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1640,50 +1608,24 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
         <v>0</v>
       </c>
     </row>
@@ -1694,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1705,37 +1647,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1743,40 +1685,40 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12287</v>
+        <v>12072</v>
       </c>
       <c r="C2">
-        <v>9245</v>
+        <v>9182</v>
       </c>
       <c r="D2">
-        <v>75.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E2">
-        <v>5074</v>
+        <v>5056</v>
       </c>
       <c r="F2">
-        <v>2208</v>
+        <v>2174</v>
       </c>
       <c r="G2">
-        <v>1128</v>
+        <v>1120</v>
       </c>
       <c r="H2">
         <v>117</v>
       </c>
       <c r="I2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K2">
         <v>61</v>
       </c>
       <c r="L2">
-        <v>1999</v>
+        <v>1968</v>
       </c>
       <c r="M2">
-        <v>1043</v>
+        <v>922</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1784,22 +1726,22 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2521</v>
+        <v>2142</v>
       </c>
       <c r="C3">
-        <v>1541</v>
+        <v>1432</v>
       </c>
       <c r="D3">
-        <v>61.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E3">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="F3">
-        <v>581</v>
+        <v>502</v>
       </c>
       <c r="G3">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="H3">
         <v>9</v>
@@ -1808,16 +1750,16 @@
         <v>58</v>
       </c>
       <c r="J3">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L3">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="M3">
-        <v>598</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1825,10 +1767,10 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C4">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D4">
         <v>63.6</v>
@@ -1840,7 +1782,7 @@
         <v>137</v>
       </c>
       <c r="G4">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -1849,7 +1791,7 @@
         <v>35</v>
       </c>
       <c r="J4">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -1907,40 +1849,40 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>717</v>
+        <v>621</v>
       </c>
       <c r="C6">
-        <v>474</v>
+        <v>307</v>
       </c>
       <c r="D6">
-        <v>66.09999999999999</v>
+        <v>49.4</v>
       </c>
       <c r="E6">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="F6">
-        <v>353</v>
+        <v>87</v>
       </c>
       <c r="G6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>237</v>
+        <v>69</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1948,40 +1890,40 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C7">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="D7">
-        <v>49.4</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="F7">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
         <v>3</v>
       </c>
-      <c r="I7">
-        <v>11</v>
-      </c>
-      <c r="J7">
-        <v>18</v>
-      </c>
       <c r="K7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="M7">
-        <v>245</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1989,40 +1931,40 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>615</v>
+        <v>303</v>
       </c>
       <c r="C8">
-        <v>258</v>
+        <v>203</v>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="E8">
-        <v>156</v>
+        <v>70</v>
       </c>
       <c r="F8">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="G8">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
         <v>3</v>
       </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
       <c r="L8">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M8">
-        <v>304</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2030,40 +1972,40 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="C9">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="D9">
-        <v>67</v>
+        <v>75.3</v>
       </c>
       <c r="E9">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F9">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G9">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M9">
-        <v>55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2071,40 +2013,40 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>227</v>
+        <v>81</v>
       </c>
       <c r="C10">
-        <v>171</v>
+        <v>62</v>
       </c>
       <c r="D10">
-        <v>75.3</v>
+        <v>76.5</v>
       </c>
       <c r="E10">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F10">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="M10">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2112,40 +2054,40 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="C11">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D11">
-        <v>76.5</v>
+        <v>56.4</v>
       </c>
       <c r="E11">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2153,37 +2095,37 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D12">
-        <v>53.3</v>
+        <v>64.5</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -2194,22 +2136,22 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>56.4</v>
+        <v>29.4</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2218,16 +2160,16 @@
         <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2235,40 +2177,40 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>64.5</v>
+        <v>68.8</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2276,28 +2218,28 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>68.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2309,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="M15">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2317,19 +2259,19 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2338,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2350,47 +2292,6 @@
         <v>1</v>
       </c>
       <c r="M16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <v>57.1</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
         <v>2</v>
       </c>
     </row>

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -572,10 +572,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="G2">
         <v>84463.36</v>
@@ -590,10 +590,10 @@
         <v>758556.46</v>
       </c>
       <c r="K2">
-        <v>21363</v>
+        <v>20959</v>
       </c>
       <c r="L2">
-        <v>27697</v>
+        <v>27691</v>
       </c>
       <c r="M2">
         <v>7966</v>
@@ -634,10 +634,10 @@
         <v>214284.85</v>
       </c>
       <c r="K3">
-        <v>7814</v>
+        <v>7424</v>
       </c>
       <c r="L3">
-        <v>4955</v>
+        <v>4952</v>
       </c>
       <c r="M3">
         <v>1535</v>
@@ -660,10 +660,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F4">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="G4">
         <v>7958.38</v>
@@ -678,10 +678,10 @@
         <v>21750.76</v>
       </c>
       <c r="K4">
-        <v>865</v>
+        <v>817</v>
       </c>
       <c r="L4">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="M4">
         <v>677</v>
@@ -722,10 +722,10 @@
         <v>27829.21</v>
       </c>
       <c r="K5">
-        <v>1301</v>
+        <v>1235</v>
       </c>
       <c r="L5">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M5">
         <v>439</v>
@@ -854,7 +854,7 @@
         <v>7461.57</v>
       </c>
       <c r="K8">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="L8">
         <v>460</v>
@@ -898,7 +898,7 @@
         <v>6637.33</v>
       </c>
       <c r="K9">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="L9">
         <v>324</v>
@@ -986,7 +986,7 @@
         <v>94.11</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>25</v>

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>product</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>Green Burner</t>
+  </si>
+  <si>
+    <t>Turmeric Ginger</t>
   </si>
   <si>
     <t>Turmeric Curcumin</t>
@@ -511,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -651,22 +654,22 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1051</v>
+        <v>1169</v>
       </c>
       <c r="C4">
-        <v>1102</v>
+        <v>1187</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>458</v>
+        <v>222</v>
       </c>
       <c r="F4">
-        <v>43.6</v>
+        <v>19.2</v>
       </c>
       <c r="G4">
-        <v>7958.38</v>
+        <v>8001.7</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -675,19 +678,19 @@
         <v>1</v>
       </c>
       <c r="J4">
-        <v>21750.76</v>
+        <v>5847.85</v>
       </c>
       <c r="K4">
-        <v>817</v>
+        <v>269</v>
       </c>
       <c r="L4">
-        <v>1765</v>
+        <v>2026</v>
       </c>
       <c r="M4">
-        <v>677</v>
+        <v>893</v>
       </c>
       <c r="N4">
-        <v>2.73</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -695,22 +698,22 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>865</v>
+        <v>1051</v>
       </c>
       <c r="C5">
-        <v>878</v>
+        <v>1102</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>630</v>
+        <v>458</v>
       </c>
       <c r="F5">
-        <v>72.8</v>
+        <v>43.6</v>
       </c>
       <c r="G5">
-        <v>7875.66</v>
+        <v>7958.38</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -719,19 +722,19 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>27829.21</v>
+        <v>21750.76</v>
       </c>
       <c r="K5">
-        <v>1235</v>
+        <v>817</v>
       </c>
       <c r="L5">
-        <v>929</v>
+        <v>1765</v>
       </c>
       <c r="M5">
-        <v>439</v>
+        <v>677</v>
       </c>
       <c r="N5">
-        <v>3.53</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -739,22 +742,22 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>621</v>
+        <v>865</v>
       </c>
       <c r="C6">
-        <v>627</v>
+        <v>878</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>396</v>
+        <v>630</v>
       </c>
       <c r="F6">
-        <v>63.8</v>
+        <v>72.8</v>
       </c>
       <c r="G6">
-        <v>3781.77</v>
+        <v>7875.66</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -763,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>718.23</v>
+        <v>27829.21</v>
       </c>
       <c r="K6">
-        <v>44</v>
+        <v>1235</v>
       </c>
       <c r="L6">
-        <v>342</v>
+        <v>929</v>
       </c>
       <c r="M6">
-        <v>236</v>
+        <v>439</v>
       </c>
       <c r="N6">
-        <v>0.19</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -783,22 +786,22 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C7">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>265</v>
+        <v>396</v>
       </c>
       <c r="F7">
-        <v>43.1</v>
+        <v>63.8</v>
       </c>
       <c r="G7">
-        <v>3738.76</v>
+        <v>3781.77</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -807,19 +810,19 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>107.47</v>
+        <v>718.23</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="L7">
-        <v>67</v>
+        <v>342</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>236</v>
       </c>
       <c r="N7">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -827,22 +830,22 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>303</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>307</v>
+        <v>619</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="F8">
-        <v>76.90000000000001</v>
+        <v>43.1</v>
       </c>
       <c r="G8">
-        <v>1494.03</v>
+        <v>3738.76</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -851,19 +854,19 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>7461.57</v>
+        <v>107.47</v>
       </c>
       <c r="K8">
-        <v>698</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>460</v>
+        <v>67</v>
       </c>
       <c r="M8">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="N8">
-        <v>4.99</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -871,22 +874,22 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="C9">
-        <v>228</v>
+        <v>307</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>190</v>
+        <v>233</v>
       </c>
       <c r="F9">
-        <v>83.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G9">
-        <v>1078.44</v>
+        <v>1494.03</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -895,19 +898,19 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>6637.33</v>
+        <v>7461.57</v>
       </c>
       <c r="K9">
-        <v>590</v>
+        <v>698</v>
       </c>
       <c r="L9">
-        <v>324</v>
+        <v>460</v>
       </c>
       <c r="M9">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c r="N9">
-        <v>6.15</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -915,22 +918,22 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="F10">
-        <v>35.8</v>
+        <v>83.7</v>
       </c>
       <c r="G10">
-        <v>610.9</v>
+        <v>1078.44</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -939,19 +942,19 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>1353.35</v>
+        <v>6637.33</v>
       </c>
       <c r="K10">
-        <v>46</v>
+        <v>590</v>
       </c>
       <c r="L10">
-        <v>146</v>
+        <v>324</v>
       </c>
       <c r="M10">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="N10">
-        <v>2.22</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -959,40 +962,43 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C11">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>82.09999999999999</v>
+        <v>35.8</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>610.9</v>
       </c>
       <c r="H11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>94.11</v>
+        <v>1353.35</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="L11">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="M11">
-        <v>16</v>
+        <v>66</v>
+      </c>
+      <c r="N11">
+        <v>2.22</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1000,40 +1006,40 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C12">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>32</v>
       </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-      <c r="E12">
-        <v>24</v>
-      </c>
       <c r="F12">
-        <v>77.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>94.11</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="M12">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1041,40 +1047,40 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C13">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F13">
-        <v>94.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
       </c>
       <c r="J13">
-        <v>26.97</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1082,43 +1088,40 @@
         <v>26</v>
       </c>
       <c r="B14">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>16</v>
       </c>
-      <c r="C14">
-        <v>16</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>14</v>
-      </c>
       <c r="F14">
-        <v>87.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G14">
-        <v>113.44</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>26.97</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M14">
-        <v>6</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1126,25 +1129,25 @@
         <v>27</v>
       </c>
       <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>14</v>
       </c>
-      <c r="C15">
-        <v>14</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>13</v>
-      </c>
       <c r="F15">
-        <v>92.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>113.44</v>
       </c>
       <c r="H15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -1156,10 +1159,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1167,39 +1173,80 @@
         <v>28</v>
       </c>
       <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>13</v>
+      </c>
+      <c r="F16">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>14</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>9</v>
+      </c>
+      <c r="M16">
         <v>7</v>
       </c>
-      <c r="C16">
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17">
         <v>7</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
+      <c r="C17">
         <v>7</v>
       </c>
-      <c r="F16">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>7</v>
+      </c>
+      <c r="F17">
         <v>100</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>7</v>
       </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <v>3</v>
       </c>
-      <c r="M16">
+      <c r="M17">
         <v>3</v>
       </c>
     </row>
@@ -1210,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1221,22 +1268,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1296,25 +1343,25 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1051</v>
+        <v>1169</v>
       </c>
       <c r="C4">
-        <v>618</v>
+        <v>891</v>
       </c>
       <c r="D4">
-        <v>280</v>
+        <v>167</v>
       </c>
       <c r="E4">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F4">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1322,22 +1369,22 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>865</v>
+        <v>1051</v>
       </c>
       <c r="C5">
-        <v>483</v>
+        <v>618</v>
       </c>
       <c r="D5">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E5">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G5">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -1348,25 +1395,25 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>621</v>
+        <v>865</v>
       </c>
       <c r="C6">
-        <v>317</v>
+        <v>483</v>
       </c>
       <c r="D6">
-        <v>217</v>
+        <v>274</v>
       </c>
       <c r="E6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1374,22 +1421,22 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C7">
-        <v>102</v>
+        <v>317</v>
       </c>
       <c r="D7">
-        <v>289</v>
+        <v>217</v>
       </c>
       <c r="E7">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="F7">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -1400,25 +1447,25 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>303</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D8">
-        <v>122</v>
+        <v>289</v>
       </c>
       <c r="E8">
-        <v>43</v>
+        <v>124</v>
       </c>
       <c r="F8">
+        <v>65</v>
+      </c>
+      <c r="G8">
         <v>29</v>
       </c>
-      <c r="G8">
-        <v>22</v>
-      </c>
       <c r="H8">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1426,25 +1473,25 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="C9">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D9">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F9">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1452,25 +1499,25 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1478,22 +1525,22 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C11">
+        <v>34</v>
+      </c>
+      <c r="D11">
+        <v>25</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11">
         <v>6</v>
-      </c>
-      <c r="D11">
-        <v>22</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1504,25 +1551,25 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1530,19 +1577,19 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C13">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
         <v>2</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1556,19 +1603,19 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1582,22 +1629,22 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1608,24 +1655,50 @@
         <v>28</v>
       </c>
       <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>6</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17">
         <v>7</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>2</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <v>3</v>
       </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <v>0</v>
       </c>
     </row>
@@ -1636,7 +1709,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1647,37 +1720,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1767,40 +1840,40 @@
         <v>16</v>
       </c>
       <c r="B4">
-        <v>1051</v>
+        <v>1169</v>
       </c>
       <c r="C4">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="D4">
-        <v>63.6</v>
+        <v>56.2</v>
       </c>
       <c r="E4">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="F4">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="G4">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>19</v>
+      </c>
+      <c r="K4">
         <v>7</v>
       </c>
-      <c r="I4">
-        <v>35</v>
-      </c>
-      <c r="J4">
-        <v>37</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
       <c r="L4">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="M4">
-        <v>174</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1808,40 +1881,40 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>865</v>
+        <v>1051</v>
       </c>
       <c r="C5">
-        <v>545</v>
+        <v>668</v>
       </c>
       <c r="D5">
-        <v>63</v>
+        <v>63.6</v>
       </c>
       <c r="E5">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="F5">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="G5">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="J5">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="M5">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1849,40 +1922,40 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>621</v>
+        <v>865</v>
       </c>
       <c r="C6">
-        <v>307</v>
+        <v>545</v>
       </c>
       <c r="D6">
-        <v>49.4</v>
+        <v>63</v>
       </c>
       <c r="E6">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="F6">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="G6">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J6">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="M6">
-        <v>245</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1890,40 +1963,40 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C7">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="D7">
-        <v>42</v>
+        <v>49.4</v>
       </c>
       <c r="E7">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="F7">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>11</v>
+      </c>
+      <c r="J7">
+        <v>18</v>
+      </c>
+      <c r="K7">
         <v>4</v>
       </c>
-      <c r="I7">
-        <v>9</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
       <c r="L7">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="M7">
-        <v>304</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -1931,40 +2004,40 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>303</v>
+        <v>615</v>
       </c>
       <c r="C8">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="D8">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="F8">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G8">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M8">
-        <v>55</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -1972,40 +2045,40 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>227</v>
+        <v>303</v>
       </c>
       <c r="C9">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="D9">
-        <v>75.3</v>
+        <v>67</v>
       </c>
       <c r="E9">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="F9">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G9">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="M9">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2013,40 +2086,40 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="C10">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="D10">
-        <v>76.5</v>
+        <v>75.3</v>
       </c>
       <c r="E10">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="M10">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2054,40 +2127,40 @@
         <v>23</v>
       </c>
       <c r="B11">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D11">
-        <v>56.4</v>
+        <v>76.5</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11">
+        <v>7</v>
+      </c>
+      <c r="H11">
         <v>3</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="M11">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2095,28 +2168,28 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C12">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12">
-        <v>64.5</v>
+        <v>56.4</v>
       </c>
       <c r="E12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
         <v>3</v>
       </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2125,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2136,40 +2209,40 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D13">
-        <v>29.4</v>
+        <v>64.5</v>
       </c>
       <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
         <v>3</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
       <c r="G13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2177,40 +2250,40 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>68.8</v>
+        <v>29.4</v>
       </c>
       <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
         <v>4</v>
       </c>
-      <c r="F14">
-        <v>4</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
       <c r="M14">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2218,28 +2291,28 @@
         <v>27</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>71.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2251,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -2259,39 +2332,80 @@
         <v>28</v>
       </c>
       <c r="B16">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17">
         <v>7</v>
       </c>
-      <c r="C16">
+      <c r="C17">
         <v>4</v>
       </c>
-      <c r="D16">
+      <c r="D17">
         <v>57.1</v>
       </c>
-      <c r="E16">
+      <c r="E17">
         <v>3</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
         <v>2</v>
       </c>
     </row>

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -575,7 +575,7 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="F2">
         <v>16.9</v>
@@ -590,16 +590,16 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>758556.46</v>
+        <v>758560.28</v>
       </c>
       <c r="K2">
         <v>20959</v>
       </c>
       <c r="L2">
-        <v>27691</v>
+        <v>27695</v>
       </c>
       <c r="M2">
-        <v>7966</v>
+        <v>7968</v>
       </c>
       <c r="N2">
         <v>8.98</v>
@@ -619,10 +619,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F3">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>13357.47</v>
@@ -634,7 +634,7 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>214284.85</v>
+        <v>214288.75</v>
       </c>
       <c r="K3">
         <v>7424</v>
@@ -643,7 +643,7 @@
         <v>4952</v>
       </c>
       <c r="M3">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="N3">
         <v>16.04</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>21750.76</v>
+        <v>21751.32</v>
       </c>
       <c r="K5">
         <v>817</v>
@@ -751,10 +751,10 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F6">
-        <v>72.8</v>
+        <v>72.7</v>
       </c>
       <c r="G6">
         <v>7875.66</v>
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>27829.21</v>
+        <v>27829.85</v>
       </c>
       <c r="K6">
         <v>1235</v>
       </c>
       <c r="L6">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="M6">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N6">
         <v>3.53</v>
@@ -810,16 +810,16 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>718.23</v>
+        <v>718.36</v>
       </c>
       <c r="K7">
         <v>44</v>
       </c>
       <c r="L7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N7">
         <v>0.19</v>
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>107.47</v>
+        <v>107.64</v>
       </c>
       <c r="K8">
         <v>7</v>
@@ -898,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>7461.57</v>
+        <v>7462.92</v>
       </c>
       <c r="K9">
         <v>698</v>
@@ -910,7 +910,7 @@
         <v>173</v>
       </c>
       <c r="N9">
-        <v>4.99</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -942,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>6637.33</v>
+        <v>6637.67</v>
       </c>
       <c r="K10">
         <v>590</v>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>94.11</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -1112,7 +1112,7 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>26.97</v>
+        <v>27.05</v>
       </c>
       <c r="K14">
         <v>3</v>
@@ -1294,10 +1294,10 @@
         <v>12072</v>
       </c>
       <c r="C2">
-        <v>9397</v>
+        <v>9423</v>
       </c>
       <c r="D2">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="E2">
         <v>408</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="H2">
-        <v>142</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1320,10 +1320,10 @@
         <v>2142</v>
       </c>
       <c r="C3">
-        <v>1185</v>
+        <v>1194</v>
       </c>
       <c r="D3">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E3">
         <v>151</v>
@@ -1335,7 +1335,7 @@
         <v>56</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1398,7 +1398,7 @@
         <v>865</v>
       </c>
       <c r="C6">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D6">
         <v>274</v>
@@ -1413,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1476,10 +1476,10 @@
         <v>303</v>
       </c>
       <c r="C9">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E9">
         <v>43</v>
@@ -1491,7 +1491,7 @@
         <v>22</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1502,7 +1502,7 @@
         <v>227</v>
       </c>
       <c r="C10">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10">
         <v>102</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -1294,10 +1294,10 @@
         <v>12072</v>
       </c>
       <c r="C2">
-        <v>9423</v>
+        <v>9429</v>
       </c>
       <c r="D2">
-        <v>1695</v>
+        <v>1700</v>
       </c>
       <c r="E2">
         <v>408</v>
@@ -1309,7 +1309,7 @@
         <v>155</v>
       </c>
       <c r="H2">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1320,10 +1320,10 @@
         <v>2142</v>
       </c>
       <c r="C3">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D3">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E3">
         <v>151</v>
@@ -1335,7 +1335,7 @@
         <v>56</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1372,10 +1372,10 @@
         <v>1051</v>
       </c>
       <c r="C5">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D5">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E5">
         <v>70</v>
@@ -1387,7 +1387,7 @@
         <v>32</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1401,7 +1401,7 @@
         <v>485</v>
       </c>
       <c r="D6">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E6">
         <v>45</v>
@@ -1413,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1427,7 +1427,7 @@
         <v>317</v>
       </c>
       <c r="D7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E7">
         <v>43</v>
@@ -1439,7 +1439,7 @@
         <v>15</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1557,7 +1557,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1569,7 +1569,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -1294,10 +1294,10 @@
         <v>12116</v>
       </c>
       <c r="C2">
-        <v>9442</v>
+        <v>9464</v>
       </c>
       <c r="D2">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="E2">
         <v>412</v>
@@ -1309,7 +1309,7 @@
         <v>156</v>
       </c>
       <c r="H2">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1320,10 +1320,10 @@
         <v>2163</v>
       </c>
       <c r="C3">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="D3">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E3">
         <v>151</v>
@@ -1335,7 +1335,7 @@
         <v>56</v>
       </c>
       <c r="H3">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1372,10 +1372,10 @@
         <v>1072</v>
       </c>
       <c r="C5">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="D5">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E5">
         <v>71</v>
@@ -1387,7 +1387,7 @@
         <v>33</v>
       </c>
       <c r="H5">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1398,7 +1398,7 @@
         <v>883</v>
       </c>
       <c r="C6">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D6">
         <v>278</v>
@@ -1413,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1424,10 +1424,10 @@
         <v>683</v>
       </c>
       <c r="C7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E7">
         <v>131</v>
@@ -1439,7 +1439,7 @@
         <v>34</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1450,7 +1450,7 @@
         <v>647</v>
       </c>
       <c r="C8">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D8">
         <v>224</v>
@@ -1465,7 +1465,7 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1476,7 +1476,7 @@
         <v>306</v>
       </c>
       <c r="C9">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9">
         <v>123</v>
@@ -1491,7 +1491,7 @@
         <v>22</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:8">

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -727,22 +727,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>829</v>
       </c>
       <c r="C7" t="n">
-        <v>687</v>
+        <v>833</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="F7" t="n">
-        <v>46.3</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>4149.48</v>
+        <v>5031.32</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -751,16 +751,16 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>196.22</v>
+        <v>239</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L7" t="n">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="M7" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="N7" t="n">
         <v>0.05</v>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>829</v>
       </c>
       <c r="C7" t="n">
         <v>125</v>
@@ -1437,7 +1437,7 @@
         <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>829</v>
       </c>
       <c r="C7" t="n">
         <v>291</v>
       </c>
       <c r="D7" t="n">
-        <v>42.6</v>
+        <v>35.1</v>
       </c>
       <c r="E7" t="n">
         <v>171</v>
@@ -2056,7 +2056,7 @@
         <v>64</v>
       </c>
       <c r="M7" t="n">
-        <v>328</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -575,10 +575,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>2087</v>
+        <v>2154</v>
       </c>
       <c r="F2">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="G2">
         <v>85527.39</v>
@@ -590,19 +590,19 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>760019.3100000001</v>
+        <v>761145.96</v>
       </c>
       <c r="K2">
-        <v>20978</v>
+        <v>20924</v>
       </c>
       <c r="L2">
-        <v>27775</v>
+        <v>27885</v>
       </c>
       <c r="M2">
-        <v>7996</v>
+        <v>8044</v>
       </c>
       <c r="N2">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -619,10 +619,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>1216</v>
+        <v>1236</v>
       </c>
       <c r="F3">
-        <v>55.6</v>
+        <v>56.5</v>
       </c>
       <c r="G3">
         <v>13645.11</v>
@@ -634,19 +634,19 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>214879.64</v>
+        <v>213298.97</v>
       </c>
       <c r="K3">
-        <v>7450</v>
+        <v>7389</v>
       </c>
       <c r="L3">
-        <v>4972</v>
+        <v>4989</v>
       </c>
       <c r="M3">
-        <v>1547</v>
+        <v>1560</v>
       </c>
       <c r="N3">
-        <v>15.75</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -663,10 +663,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F4">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="G4">
         <v>8001.7</v>
@@ -684,7 +684,7 @@
         <v>269</v>
       </c>
       <c r="L4">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="M4">
         <v>893</v>
@@ -707,10 +707,10 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>479</v>
+        <v>501</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>8219.58</v>
@@ -722,19 +722,19 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>21784.62</v>
+        <v>22150.88</v>
       </c>
       <c r="K5">
-        <v>817</v>
+        <v>830</v>
       </c>
       <c r="L5">
-        <v>1781</v>
+        <v>1816</v>
       </c>
       <c r="M5">
-        <v>683</v>
+        <v>705</v>
       </c>
       <c r="N5">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -751,10 +751,10 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="F6">
-        <v>70.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="G6">
         <v>8180.64</v>
@@ -766,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>27418.47</v>
+        <v>27002.14</v>
       </c>
       <c r="K6">
-        <v>1213</v>
+        <v>1181</v>
       </c>
       <c r="L6">
-        <v>930</v>
+        <v>896</v>
       </c>
       <c r="M6">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -795,10 +795,10 @@
         <v>2</v>
       </c>
       <c r="E7">
-        <v>359</v>
+        <v>404</v>
       </c>
       <c r="F7">
-        <v>42.3</v>
+        <v>47.6</v>
       </c>
       <c r="G7">
         <v>5211.19</v>
@@ -810,19 +810,19 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>196.22</v>
+        <v>441.17</v>
       </c>
       <c r="K7">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L7">
-        <v>87</v>
+        <v>177</v>
       </c>
       <c r="M7">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="N7">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -839,10 +839,10 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="F8">
-        <v>63.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G8">
         <v>4129.07</v>
@@ -854,19 +854,19 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>742.65</v>
+        <v>1081.88</v>
       </c>
       <c r="K8">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="L8">
-        <v>379</v>
+        <v>474</v>
       </c>
       <c r="M8">
-        <v>261</v>
+        <v>312</v>
       </c>
       <c r="N8">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -883,10 +883,10 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F9">
-        <v>75.2</v>
+        <v>74.5</v>
       </c>
       <c r="G9">
         <v>1547.49</v>
@@ -898,19 +898,19 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>7911.85</v>
+        <v>8259.040000000001</v>
       </c>
       <c r="K9">
-        <v>742</v>
+        <v>780</v>
       </c>
       <c r="L9">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="M9">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="N9">
-        <v>5.11</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -942,19 +942,19 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>6488.87</v>
+        <v>5492.87</v>
       </c>
       <c r="K10">
-        <v>581</v>
+        <v>486</v>
       </c>
       <c r="L10">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="M10">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="N10">
-        <v>5.81</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -971,10 +971,10 @@
         <v>2</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>37</v>
+        <v>39.5</v>
       </c>
       <c r="G11">
         <v>610.9</v>
@@ -1015,10 +1015,10 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1030,16 +1030,16 @@
         <v>1</v>
       </c>
       <c r="J12">
-        <v>163.25</v>
+        <v>381.21</v>
       </c>
       <c r="K12">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L12">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M12">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1056,10 +1056,10 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>75.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="L13">
+        <v>12</v>
+      </c>
+      <c r="M13">
         <v>11</v>
-      </c>
-      <c r="M13">
-        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1156,10 +1156,10 @@
         <v>1</v>
       </c>
       <c r="J15">
-        <v>27.05</v>
+        <v>37.02</v>
       </c>
       <c r="K15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1294,7 +1294,7 @@
         <v>12195</v>
       </c>
       <c r="C2">
-        <v>9515</v>
+        <v>9516</v>
       </c>
       <c r="D2">
         <v>1745</v>
@@ -1309,7 +1309,7 @@
         <v>157</v>
       </c>
       <c r="H2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1372,7 +1372,7 @@
         <v>1089</v>
       </c>
       <c r="C5">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D5">
         <v>292</v>
@@ -1387,7 +1387,7 @@
         <v>33</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1427,7 +1427,7 @@
         <v>147</v>
       </c>
       <c r="D7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E7">
         <v>151</v>
@@ -1439,7 +1439,7 @@
         <v>38</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -1294,10 +1294,10 @@
         <v>12226</v>
       </c>
       <c r="C2">
-        <v>9527</v>
+        <v>9531</v>
       </c>
       <c r="D2">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="E2">
         <v>415</v>
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="H2">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1320,7 +1320,7 @@
         <v>2194</v>
       </c>
       <c r="C3">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D3">
         <v>656</v>
@@ -1335,7 +1335,7 @@
         <v>57</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1372,7 +1372,7 @@
         <v>1094</v>
       </c>
       <c r="C5">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D5">
         <v>295</v>
@@ -1387,7 +1387,7 @@
         <v>33</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1398,7 +1398,7 @@
         <v>905</v>
       </c>
       <c r="C6">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D6">
         <v>288</v>
@@ -1413,7 +1413,7 @@
         <v>22</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1450,10 +1450,10 @@
         <v>677</v>
       </c>
       <c r="C8">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D8">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E8">
         <v>44</v>
@@ -1465,7 +1465,7 @@
         <v>19</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">

--- a/product_deepdive.xlsx
+++ b/product_deepdive.xlsx
@@ -69,10 +69,10 @@
     <t>Turmeric Ginger</t>
   </si>
   <si>
+    <t>Advent Calendar</t>
+  </si>
+  <si>
     <t>Turmeric Curcumin</t>
-  </si>
-  <si>
-    <t>Advent Calendar</t>
   </si>
   <si>
     <t>Gut Shift</t>
@@ -566,22 +566,22 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12239</v>
+        <v>12255</v>
       </c>
       <c r="C2">
-        <v>14572</v>
+        <v>14613</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2">
-        <v>2167</v>
+        <v>2195</v>
       </c>
       <c r="F2">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="G2">
-        <v>85868.78999999999</v>
+        <v>86105.7</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -590,19 +590,19 @@
         <v>1</v>
       </c>
       <c r="J2">
-        <v>761317.5</v>
+        <v>759893.6899999999</v>
       </c>
       <c r="K2">
-        <v>20897</v>
+        <v>20792</v>
       </c>
       <c r="L2">
-        <v>27888</v>
+        <v>27884</v>
       </c>
       <c r="M2">
-        <v>8044</v>
+        <v>8056</v>
       </c>
       <c r="N2">
-        <v>8.869999999999999</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -610,22 +610,22 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2197</v>
+        <v>2202</v>
       </c>
       <c r="C3">
-        <v>2418</v>
+        <v>2427</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="F3">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
       <c r="G3">
-        <v>13701.51</v>
+        <v>13752.27</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -634,19 +634,19 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>213259.99</v>
+        <v>213330.03</v>
       </c>
       <c r="K3">
-        <v>7381</v>
+        <v>7380</v>
       </c>
       <c r="L3">
-        <v>5005</v>
+        <v>5007</v>
       </c>
       <c r="M3">
-        <v>1564</v>
+        <v>1560</v>
       </c>
       <c r="N3">
-        <v>15.56</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -663,10 +663,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F4">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="G4">
         <v>8001.7</v>
@@ -698,22 +698,22 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>1096</v>
+        <v>1112</v>
       </c>
       <c r="C5">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="F5">
-        <v>46.4</v>
+        <v>47.9</v>
       </c>
       <c r="G5">
-        <v>8265.290000000001</v>
+        <v>7356.93</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -722,19 +722,19 @@
         <v>1</v>
       </c>
       <c r="J5">
-        <v>22311.62</v>
+        <v>780.8</v>
       </c>
       <c r="K5">
-        <v>834</v>
+        <v>50</v>
       </c>
       <c r="L5">
-        <v>1823</v>
+        <v>381</v>
       </c>
       <c r="M5">
-        <v>710</v>
+        <v>259</v>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -742,22 +742,22 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>958</v>
+        <v>1104</v>
       </c>
       <c r="C6">
-        <v>986</v>
+        <v>1157</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>460</v>
+        <v>517</v>
       </c>
       <c r="F6">
-        <v>48</v>
+        <v>46.8</v>
       </c>
       <c r="G6">
-        <v>6252.53</v>
+        <v>8317.530000000001</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -766,19 +766,19 @@
         <v>1</v>
       </c>
       <c r="J6">
-        <v>646.6</v>
+        <v>22364.88</v>
       </c>
       <c r="K6">
-        <v>42</v>
+        <v>833</v>
       </c>
       <c r="L6">
-        <v>258</v>
+        <v>1831</v>
       </c>
       <c r="M6">
-        <v>183</v>
+        <v>721</v>
       </c>
       <c r="N6">
-        <v>0.1</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -786,22 +786,22 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C7">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="F7">
-        <v>71.5</v>
+        <v>70.8</v>
       </c>
       <c r="G7">
-        <v>8252.4</v>
+        <v>8279.309999999999</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -810,19 +810,19 @@
         <v>1</v>
       </c>
       <c r="J7">
-        <v>27109.3</v>
+        <v>26998.58</v>
       </c>
       <c r="K7">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="L7">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="M7">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="N7">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -830,22 +830,22 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C8">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="F8">
-        <v>70.7</v>
+        <v>71.3</v>
       </c>
       <c r="G8">
-        <v>4191.26</v>
+        <v>4249.85</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -854,19 +854,19 @@
         <v>1</v>
       </c>
       <c r="J8">
-        <v>1266.2</v>
+        <v>1418.28</v>
       </c>
       <c r="K8">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="L8">
-        <v>490</v>
+        <v>512</v>
       </c>
       <c r="M8">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="N8">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -874,22 +874,22 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C9">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F9">
-        <v>74.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="G9">
-        <v>1566.93</v>
+        <v>1596.09</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -898,19 +898,19 @@
         <v>1</v>
       </c>
       <c r="J9">
-        <v>8385.469999999999</v>
+        <v>8640.08</v>
       </c>
       <c r="K9">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="L9">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="M9">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="N9">
-        <v>5.35</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -918,22 +918,22 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C10">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F10">
-        <v>83</v>
+        <v>81.3</v>
       </c>
       <c r="G10">
-        <v>1116.28</v>
+        <v>1144.66</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -942,19 +942,19 @@
         <v>1</v>
       </c>
       <c r="J10">
-        <v>5097.18</v>
+        <v>5390.63</v>
       </c>
       <c r="K10">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="L10">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M10">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="N10">
-        <v>4.57</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1006,34 +1006,34 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12">
-        <v>87.5</v>
+        <v>87.8</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
       <c r="J12">
-        <v>419.31</v>
+        <v>578.6799999999999</v>
       </c>
       <c r="K12">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L12">
         <v>32</v>
@@ -1047,10 +1047,10 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1059,13 +1059,13 @@
         <v>28</v>
       </c>
       <c r="F13">
-        <v>75.7</v>
+        <v>73.7</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M13">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1088,22 +1088,22 @@
         <v>26</v>
       </c>
       <c r="B14">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>21</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>18</v>
       </c>
-      <c r="C14">
-        <v>19</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>16</v>
-      </c>
       <c r="F14">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="G14">
-        <v>134.71</v>
+        <v>148.89</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1173,25 +1173,25 @@
         <v>28</v>
       </c>
       <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
         <v>15</v>
       </c>
-      <c r="C16">
-        <v>15</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>14</v>
-      </c>
       <c r="F16">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -1291,16 +1291,16 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12239</v>
+        <v>12255</v>
       </c>
       <c r="C2">
-        <v>9543</v>
+        <v>9545</v>
       </c>
       <c r="D2">
-        <v>1757</v>
+        <v>1766</v>
       </c>
       <c r="E2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F2">
         <v>280</v>
@@ -1309,7 +1309,7 @@
         <v>158</v>
       </c>
       <c r="H2">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1317,13 +1317,13 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2197</v>
+        <v>2202</v>
       </c>
       <c r="C3">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="D3">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E3">
         <v>153</v>
@@ -1335,7 +1335,7 @@
         <v>57</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1369,25 +1369,25 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>1096</v>
+        <v>1112</v>
       </c>
       <c r="C5">
-        <v>646</v>
+        <v>227</v>
       </c>
       <c r="D5">
-        <v>297</v>
+        <v>561</v>
       </c>
       <c r="E5">
-        <v>72</v>
+        <v>165</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="G5">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1395,25 +1395,25 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>958</v>
+        <v>1104</v>
       </c>
       <c r="C6">
-        <v>183</v>
+        <v>648</v>
       </c>
       <c r="D6">
-        <v>479</v>
+        <v>301</v>
       </c>
       <c r="E6">
-        <v>162</v>
+        <v>72</v>
       </c>
       <c r="F6">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G6">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1421,13 +1421,13 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E7">
         <v>47</v>
@@ -1439,7 +1439,7 @@
         <v>22</v>
       </c>
       <c r="H7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1447,25 +1447,25 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C8">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E8">
         <v>44</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>20</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1473,25 +1473,25 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C9">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E9">
         <v>44</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9">
         <v>23</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1499,16 +1499,16 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C10">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>16</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1551,13 +1551,13 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>7</v>
       </c>
       <c r="D12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -1577,10 +1577,10 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <v>14</v>
@@ -1603,13 +1603,13 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1655,7 +1655,7 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>6</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1758,19 +1758,19 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>12239</v>
+        <v>12255</v>
       </c>
       <c r="C2">
-        <v>9188</v>
+        <v>9189</v>
       </c>
       <c r="D2">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="E2">
         <v>5059</v>
       </c>
       <c r="F2">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="G2">
         <v>1120</v>
@@ -1791,7 +1791,7 @@
         <v>1969</v>
       </c>
       <c r="M2">
-        <v>1082</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>2197</v>
+        <v>2202</v>
       </c>
       <c r="C3">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="D3">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E3">
         <v>556</v>
       </c>
       <c r="F3">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G3">
         <v>245</v>
@@ -1829,10 +1829,10 @@
         <v>11</v>
       </c>
       <c r="L3">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M3">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1881,40 +1881,40 @@
         <v>17</v>
       </c>
       <c r="B5">
-        <v>1096</v>
+        <v>1112</v>
       </c>
       <c r="C5">
-        <v>674</v>
+        <v>432</v>
       </c>
       <c r="D5">
-        <v>61.5</v>
+        <v>38.8</v>
       </c>
       <c r="E5">
-        <v>342</v>
+        <v>253</v>
       </c>
       <c r="F5">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="G5">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="H5">
         <v>7</v>
       </c>
       <c r="I5">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>214</v>
+        <v>97</v>
       </c>
       <c r="M5">
-        <v>208</v>
+        <v>583</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1922,40 +1922,40 @@
         <v>18</v>
       </c>
       <c r="B6">
-        <v>958</v>
+        <v>1104</v>
       </c>
       <c r="C6">
-        <v>395</v>
+        <v>676</v>
       </c>
       <c r="D6">
-        <v>41.2</v>
+        <v>61.2</v>
       </c>
       <c r="E6">
-        <v>234</v>
+        <v>342</v>
       </c>
       <c r="F6">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="G6">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>35</v>
+      </c>
+      <c r="J6">
+        <v>37</v>
+      </c>
+      <c r="K6">
         <v>4</v>
       </c>
-      <c r="I6">
-        <v>14</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
       <c r="L6">
-        <v>86</v>
+        <v>214</v>
       </c>
       <c r="M6">
-        <v>477</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1963,10 +1963,10 @@
         <v>19</v>
       </c>
       <c r="B7">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C7">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D7">
         <v>61.4</v>
@@ -1978,13 +1978,13 @@
         <v>191</v>
       </c>
       <c r="G7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H7">
         <v>5</v>
       </c>
       <c r="I7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7">
         <v>26</v>
@@ -1996,7 +1996,7 @@
         <v>158</v>
       </c>
       <c r="M7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2004,19 +2004,19 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C8">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D8">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="E8">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F8">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G8">
         <v>57</v>
@@ -2034,10 +2034,10 @@
         <v>4</v>
       </c>
       <c r="L8">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M8">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2045,19 +2045,19 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C9">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D9">
-        <v>65.3</v>
+        <v>64.7</v>
       </c>
       <c r="E9">
         <v>71</v>
       </c>
       <c r="F9">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9">
         <v>35</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -2075,10 +2075,10 @@
         <v>3</v>
       </c>
       <c r="L9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2086,19 +2086,19 @@
         <v>22</v>
       </c>
       <c r="B10">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C10">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D10">
-        <v>73.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="E10">
         <v>53</v>
       </c>
       <c r="F10">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G10">
         <v>22</v>
@@ -2107,7 +2107,7 @@
         <v>2</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -2116,10 +2116,10 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M10">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2168,13 +2168,13 @@
         <v>24</v>
       </c>
       <c r="B12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>22</v>
       </c>
       <c r="D12">
-        <v>55</v>
+        <v>53.7</v>
       </c>
       <c r="E12">
         <v>12</v>
@@ -2201,7 +2201,7 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2209,19 +2209,19 @@
         <v>25</v>
       </c>
       <c r="B13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>6</v>
@@ -2250,16 +2250,16 @@
         <v>26</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14">
-        <v>72.2</v>
+        <v>70</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -2283,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2332,13 +2332,13 @@
         <v>28</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>66.7</v>
+        <v>68.8</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -2347,7 +2347,7 @@
         <v>6</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
